--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,17 +484,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nada</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -514,17 +509,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010250014</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -534,12 +529,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -549,42 +544,1727 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3918786000010254032</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>18145</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3918786000010254030</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>1 Sessão</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3918786000010252002</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>17585</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3918786000010254028</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3918786000010254026</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>13845</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3918786000010254024</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3918786000010254022</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3918786000010254020</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3918786000010254018</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9565</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3918786000010254016</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>8065</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3918786000010254014</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3918786000010254012</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4455</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3918786000010254010</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3918786000010254008</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compra de 3 pratos </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3918786000010254006</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3918786000010254004</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3918786000010250004</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>WIKHALIHERA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>WIKHALIHERA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3918786000010254002</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -849,13 +2529,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A2AD10-923F-454F-AAFD-DE68639D7C28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{392BE2BC-BDEB-4D6C-8D3E-D2B97F97C516}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414B9C67-B917-4FA4-8CD9-E2AC262CC649}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F97496F9-18D6-4E56-BB56-173E0B9F2D8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D21B4C37-C9CF-46AF-BB5D-441FD219F47D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED42028-C3EA-4283-893B-3D3F275E45C0}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,47 +484,52 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -534,59 +539,59 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3918786000010254032</t>
+          <t>3918786000010260006</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -596,17 +601,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -616,89 +626,89 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3918786000010254030</t>
+          <t>3918786000010260004</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -708,17 +718,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -728,22 +743,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -753,52 +768,52 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3918786000010254028</t>
+          <t>3918786000010260002</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -810,7 +825,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -820,17 +835,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -840,22 +860,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -865,64 +885,64 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3918786000010254026</t>
+          <t>3918786000010254098</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -932,17 +952,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -952,22 +977,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -977,17 +1002,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -997,7 +1022,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1007,34 +1032,34 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3918786000010254024</t>
+          <t>3918786000010254096</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1044,17 +1069,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1064,62 +1094,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1129,24 +1159,24 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3918786000010254022</t>
+          <t>3918786000010254094</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1156,17 +1186,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1176,22 +1211,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1201,37 +1236,37 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1241,24 +1276,24 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3918786000010254020</t>
+          <t>3918786000010254092</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,17 +1303,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NACARROANE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1288,22 +1328,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1313,27 +1353,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1343,7 +1383,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1353,24 +1393,24 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3918786000010254018</t>
+          <t>3918786000010254090</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1380,67 +1420,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NACARROANE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3918786000010254048</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Somos Caz 2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Somos Caz 2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3918786000010250006</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>MUATHUNAKA</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>MUATHUNAKA</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1450,39 +1495,39 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3918786000010254016</t>
+          <t>3918786000010254088</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>940</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1492,47 +1537,52 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NACARROANE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1542,59 +1592,59 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3918786000010254014</t>
+          <t>3918786000010254086</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1604,109 +1654,114 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NACARROANE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3918786000010254012</t>
+          <t>3918786000010254084</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1716,17 +1771,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1736,22 +1796,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1766,59 +1826,59 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>45800</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Aurélio António</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>4 Sessão</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>48925</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3918786000010254010</t>
+          <t>3918786000010254082</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1828,17 +1888,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1848,22 +1913,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1873,89 +1938,89 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3918786000010254008</t>
+          <t>3918786000010254080</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compra de 3 pratos </t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1965,22 +2030,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1990,57 +2055,57 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>3918786000010254006</t>
+          <t>3918786000010254078</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -2057,17 +2122,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2077,22 +2147,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2102,167 +2172,3373 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>3918786000010254004</t>
+          <t>3918786000010254076</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8900</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3918786000010254044</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>42400</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>43645</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3918786000010254074</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3918786000010254044</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>42400</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>41905</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3918786000010254072</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8300</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3918786000010254044</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Poupança da Sorte</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>42400</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>41905</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>3918786000010254070</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7980</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3918786000010254036</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>42400</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>40735</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>3918786000010254068</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7980</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3918786000010254036</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>41900</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>39665</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>3918786000010254066</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7660</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3918786000010254036</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>39400</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>38675</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>3918786000010254064</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>28-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3918786000010254036</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Wiwanana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>39400</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>36875</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3918786000010254062</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6880</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>13900</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>34125</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>3918786000010254060</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>31665</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>3918786000010254058</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>29325</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>3918786000010254056</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>26615</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3918786000010254054</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>23725</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>3918786000010254052</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21145</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>3918786000010254050</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>3918786000010254032</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>18145</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>3918786000010254030</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>17585</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>3918786000010254028</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>3918786000010254026</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>13845</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>3918786000010254024</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>3918786000010254022</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>3918786000010254020</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>3918786000010254018</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>9565</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>3918786000010254016</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>8065</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>3918786000010254014</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3918786000010254012</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4455</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3918786000010254010</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3918786000010254008</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compra de 3 pratos </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3918786000010254006</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3918786000010254004</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>JARDIM</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>3918786000010250004</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>Aurélio António</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>1 Sessão</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>405</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
         <is>
           <t>3918786000010254002</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -2271,271 +5547,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{392BE2BC-BDEB-4D6C-8D3E-D2B97F97C516}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F97496F9-18D6-4E56-BB56-173E0B9F2D8E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED42028-C3EA-4283-893B-3D3F275E45C0}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,114 +484,109 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250018</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>67165</t>
+          <t>76175</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3918786000010260006</t>
+          <t>3918786000010263168</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -601,22 +596,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -626,89 +616,89 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>13250</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>74555</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3918786000010263166</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2290</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>64875</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>3918786000010260004</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,22 +708,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -743,22 +728,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -768,64 +753,64 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>73325</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3918786000010260002</t>
+          <t>3918786000010263164</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -835,22 +820,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -860,22 +840,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -885,64 +865,64 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>8 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13250</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>72795</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3918786000010263162</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>61795</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3918786000010254098</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -952,22 +932,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -977,22 +952,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010254042</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1002,17 +977,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>58700</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1022,44 +997,44 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3918786000010254096</t>
+          <t>3918786000010263160</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1069,114 +1044,109 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>9 Sessão</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58465</t>
+          <t>70810</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3918786000010254094</t>
+          <t>3918786000010262006</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,114 +1156,109 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3918786000010254092</t>
+          <t>3918786000010262004</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1303,22 +1268,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1328,22 +1288,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010250004</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1353,17 +1313,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1373,44 +1333,44 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3918786000010254090</t>
+          <t>3918786000010262002</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1420,12 +1380,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1435,12 +1395,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1450,22 +1410,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1475,7 +1435,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1485,49 +1445,49 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3918786000010254088</t>
+          <t>3918786000010260006</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1537,12 +1497,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,7 +1512,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1567,22 +1527,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1552,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1602,12 +1562,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1617,34 +1577,34 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3918786000010254086</t>
+          <t>3918786000010260004</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1654,12 +1614,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1669,7 +1629,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1684,17 +1644,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1719,49 +1679,49 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3918786000010254084</t>
+          <t>3918786000010260002</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1771,7 +1731,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1786,7 +1746,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1836,12 +1796,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1856,29 +1816,29 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3918786000010254082</t>
+          <t>3918786000010254098</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1888,12 +1848,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1903,7 +1863,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1918,17 +1878,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1938,12 +1898,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1953,7 +1913,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1963,39 +1923,39 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>47635</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3918786000010254080</t>
+          <t>3918786000010254096</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2005,12 +1965,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2020,7 +1980,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2035,32 +1995,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2070,12 +2030,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2085,7 +2045,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2095,24 +2055,24 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>3918786000010254078</t>
+          <t>3918786000010254094</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,12 +2082,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2137,7 +2097,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2152,17 +2112,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2172,12 +2132,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2187,12 +2147,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2202,7 +2162,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2212,24 +2172,24 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>45155</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>3918786000010254076</t>
+          <t>3918786000010254092</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2239,12 +2199,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2254,7 +2214,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2269,17 +2229,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2289,12 +2249,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2304,12 +2264,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2319,7 +2279,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2329,24 +2289,24 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>43645</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3918786000010254074</t>
+          <t>3918786000010254090</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2356,12 +2316,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2371,7 +2331,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2386,17 +2346,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2411,7 +2371,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2421,49 +2381,49 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>54940</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3918786000010254088</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>41905</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>3918786000010254072</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>940</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2473,12 +2433,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2488,7 +2448,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2503,17 +2463,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2528,7 +2488,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2538,12 +2498,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2553,7 +2513,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2563,24 +2523,24 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>3918786000010254070</t>
+          <t>3918786000010254086</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,12 +2550,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2605,47 +2565,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3918786000010254046</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Somos Capaz</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Somos Capaz</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Ribaue</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3918786000010254036</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2655,12 +2615,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2670,7 +2630,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2680,39 +2640,39 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3918786000010254068</t>
+          <t>3918786000010254084</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2722,7 +2682,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2737,17 +2697,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2762,7 +2722,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2772,7 +2732,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2782,12 +2742,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2797,24 +2757,24 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>48925</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3918786000010254066</t>
+          <t>3918786000010254082</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2824,12 +2784,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2839,7 +2799,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2854,17 +2814,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2874,12 +2834,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2889,22 +2849,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2914,24 +2874,24 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>3918786000010254064</t>
+          <t>3918786000010254080</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2941,12 +2901,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2956,7 +2916,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2971,17 +2931,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2991,12 +2951,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3006,7 +2966,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3021,7 +2981,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3031,24 +2991,24 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3918786000010254062</t>
+          <t>3918786000010254078</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3058,12 +3018,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3073,7 +3033,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3088,17 +3048,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3108,12 +3068,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3123,22 +3083,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3148,24 +3108,24 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3918786000010254060</t>
+          <t>3918786000010254076</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3175,12 +3135,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3190,7 +3150,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3205,17 +3165,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3225,12 +3185,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3240,12 +3200,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3255,7 +3215,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3265,24 +3225,24 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3918786000010254058</t>
+          <t>3918786000010254074</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3292,12 +3252,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3307,7 +3267,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3322,17 +3282,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3342,12 +3302,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3357,12 +3317,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3372,7 +3332,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3382,24 +3342,24 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>3918786000010254056</t>
+          <t>3918786000010254072</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3409,12 +3369,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3424,7 +3384,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3439,17 +3399,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3459,12 +3419,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3474,7 +3434,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3489,7 +3449,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3499,24 +3459,24 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>26615</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>3918786000010254054</t>
+          <t>3918786000010254070</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3526,12 +3486,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3541,12 +3501,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3556,17 +3516,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3576,12 +3536,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3591,64 +3551,64 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>40735</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>3918786000010254068</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>23725</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>3918786000010254052</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3658,7 +3618,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>12-May-2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3673,17 +3633,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3698,7 +3658,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3708,22 +3668,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3733,24 +3693,24 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3918786000010254050</t>
+          <t>3918786000010254066</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3760,17 +3720,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3780,22 +3745,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3810,22 +3775,22 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3835,7 +3800,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3845,24 +3810,24 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3918786000010254032</t>
+          <t>3918786000010254064</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3872,17 +3837,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3892,22 +3862,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3917,37 +3887,37 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3957,24 +3927,24 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3918786000010254030</t>
+          <t>3918786000010254062</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3984,17 +3954,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4004,22 +3979,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4029,37 +4004,37 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4069,24 +4044,24 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3918786000010254028</t>
+          <t>3918786000010254060</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4096,17 +4071,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4116,22 +4096,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4146,32 +4126,32 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4181,24 +4161,24 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3918786000010254026</t>
+          <t>3918786000010254058</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4208,17 +4188,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>01-May-2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4228,22 +4213,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4253,27 +4238,27 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4283,7 +4268,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4293,24 +4278,24 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3918786000010254024</t>
+          <t>3918786000010254056</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4320,17 +4305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4340,22 +4330,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4365,17 +4355,17 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4385,17 +4375,17 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4405,24 +4395,24 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3918786000010254022</t>
+          <t>3918786000010254054</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>700</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4432,17 +4422,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4452,22 +4447,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4477,17 +4472,17 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>94</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4497,17 +4492,17 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4517,24 +4512,24 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>3918786000010254020</t>
+          <t>3918786000010254052</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4544,17 +4539,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4564,22 +4564,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4589,17 +4589,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4629,24 +4629,24 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3918786000010254018</t>
+          <t>3918786000010254050</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4656,57 +4656,57 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3918786000010250006</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>MUATHUNAKA</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>MUATHUNAKA</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4716,49 +4716,49 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3918786000010254016</t>
+          <t>3918786000010254032</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4768,22 +4768,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4793,32 +4793,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4828,49 +4828,49 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>3918786000010254014</t>
+          <t>3918786000010254030</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4880,22 +4880,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4905,32 +4905,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>58800</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4940,49 +4940,49 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>3918786000010254012</t>
+          <t>3918786000010254028</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5017,17 +5017,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250010</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5037,64 +5037,64 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Aurélio António</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>4 Sessão</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>3918786000010254010</t>
+          <t>3918786000010254026</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250010</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5164,74 +5164,69 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>3918786000010254008</t>
+          <t>3918786000010254024</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compra de 3 pratos </t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5246,17 +5241,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250012</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5266,12 +5261,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -5281,49 +5276,49 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>3918786000010254006</t>
+          <t>3918786000010254022</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5333,17 +5328,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5358,17 +5353,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250012</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5378,12 +5373,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -5393,152 +5388,1058 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>3918786000010254004</t>
+          <t>3918786000010254020</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3918786000010254018</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>13150</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>68680</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3918786000010254016</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>53100</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>68480</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>3918786000010254014</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16295</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>54300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>68340</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>3918786000010254012</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>55300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>69280</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>3918786000010254010</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16445</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>68910</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>3918786000010254008</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16425</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compra de 3 pratos </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>69120</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>3918786000010254006</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16565</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>69010</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>3918786000010254004</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>JARDIM</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>compra de pratos</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>3918786000010250004</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>54600</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>Aurélio António</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>1 Sessão</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>68665</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
         <is>
           <t>3918786000010254002</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -5547,4 +6448,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9032BAA0-63C6-48D6-9B52-7585075162D7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{821690EC-8550-4A59-A6ED-185A56947E0E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2EDBB8B-3EC3-40A7-B256-69E4844328C9}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,17 +484,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -504,22 +509,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010250018</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FUTURO MELHOR</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FUTURO MELHOR</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -529,64 +534,64 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>91685</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3918786000010263168</t>
+          <t>3918786000010267348</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>680</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -596,17 +601,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -616,22 +626,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010250014</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -641,64 +651,64 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>60900</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3918786000010263166</t>
+          <t>3918786000010267346</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -708,17 +718,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -728,22 +743,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010250016</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -753,64 +768,64 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>73325</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3918786000010263164</t>
+          <t>3918786000010266048</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -820,17 +835,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -840,22 +860,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010250016</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -865,64 +885,64 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72795</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3918786000010263162</t>
+          <t>3918786000010266046</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -932,82 +952,87 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NAMALE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010250014</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1017,24 +1042,24 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>72295</t>
+          <t>84605</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3918786000010263160</t>
+          <t>3918786000010266044</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1044,109 +1069,114 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMALE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70810</t>
+          <t>82605</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3918786000010262006</t>
+          <t>3918786000010266042</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1156,109 +1186,114 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMALE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>66900</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>53200</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Aurélio António</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>8 Sessão</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>68670</t>
+          <t>81505</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3918786000010262004</t>
+          <t>3918786000010266040</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,17 +1303,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>NAMALE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1288,22 +1328,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010250004</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WIKHALIHERA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WIKHALIHERA</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1313,64 +1353,64 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3918786000010262002</t>
+          <t>3918786000010266038</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1380,12 +1420,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1395,12 +1435,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1410,22 +1450,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1435,7 +1475,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1445,49 +1485,49 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>67165</t>
+          <t>79005</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3918786000010260006</t>
+          <t>3918786000010266036</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1497,12 +1537,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1512,7 +1552,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1527,32 +1567,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1562,12 +1602,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1577,34 +1617,34 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3918786000010260004</t>
+          <t>3918786000010266034</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,12 +1654,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1629,7 +1669,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1644,17 +1684,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1664,12 +1704,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1679,49 +1719,49 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3918786000010260002</t>
+          <t>3918786000010266032</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1731,12 +1771,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1746,7 +1786,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1761,17 +1801,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1786,7 +1826,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1796,12 +1836,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1811,34 +1851,34 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3918786000010254098</t>
+          <t>3918786000010266030</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1848,22 +1888,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1873,22 +1908,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010254042</t>
+          <t>3918786000010250018</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1898,17 +1933,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1918,44 +1953,44 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>76175</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3918786000010254096</t>
+          <t>3918786000010263168</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1965,22 +2000,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1990,42 +2020,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2035,44 +2065,44 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>58465</t>
+          <t>74555</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>3918786000010254094</t>
+          <t>3918786000010263166</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2082,22 +2112,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2107,22 +2132,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2132,64 +2157,64 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>73325</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>3918786000010254092</t>
+          <t>3918786000010263164</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2199,22 +2224,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2224,22 +2244,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2249,52 +2269,52 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3918786000010254090</t>
+          <t>3918786000010263162</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2306,7 +2326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2316,22 +2336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2341,22 +2356,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2366,17 +2381,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>58700</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2386,32 +2401,32 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>3918786000010254088</t>
+          <t>3918786000010263160</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2423,7 +2438,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2433,114 +2448,109 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>9 Sessão</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>70810</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>3918786000010254086</t>
+          <t>3918786000010262006</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2550,114 +2560,109 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3918786000010254084</t>
+          <t>3918786000010262004</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2667,22 +2672,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2692,22 +2692,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250004</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2717,64 +2717,64 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3918786000010254082</t>
+          <t>3918786000010262002</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2814,32 +2814,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2859,39 +2859,39 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>47635</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>3918786000010254080</t>
+          <t>3918786000010260006</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2981,34 +2981,34 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3918786000010254078</t>
+          <t>3918786000010260004</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3093,39 +3093,39 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>45155</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3918786000010254076</t>
+          <t>3918786000010260002</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3215,34 +3215,34 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>43645</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3918786000010254074</t>
+          <t>3918786000010254098</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3332,34 +3332,34 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>3918786000010254072</t>
+          <t>3918786000010254096</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3399,22 +3399,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>3918786000010254070</t>
+          <t>3918786000010254094</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3501,47 +3501,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3918786000010254040</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Inthela</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Inthela</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Ribaue</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3918786000010254036</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3576,39 +3576,39 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>3918786000010254068</t>
+          <t>3918786000010254092</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3668,22 +3668,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3693,24 +3693,24 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3918786000010254066</t>
+          <t>3918786000010254090</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3785,22 +3785,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3810,24 +3810,24 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3918786000010254064</t>
+          <t>3918786000010254088</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>940</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3927,24 +3927,24 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3918786000010254062</t>
+          <t>3918786000010254086</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3984,17 +3984,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4044,24 +4044,24 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3918786000010254060</t>
+          <t>3918786000010254084</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4136,49 +4136,49 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>48925</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>3918786000010254082</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2460</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>31665</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3918786000010254058</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4218,17 +4218,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3918786000010254056</t>
+          <t>3918786000010254080</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4395,24 +4395,24 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>26615</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3918786000010254054</t>
+          <t>3918786000010254078</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4452,17 +4452,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4512,24 +4512,24 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>3918786000010254052</t>
+          <t>3918786000010254076</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4604,49 +4604,49 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>43645</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>3918786000010254074</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2580</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>21145</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3918786000010254050</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4656,17 +4656,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4676,22 +4681,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4706,32 +4711,32 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4741,24 +4746,24 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3918786000010254032</t>
+          <t>3918786000010254072</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4768,17 +4773,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4788,22 +4798,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4813,37 +4823,37 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4853,24 +4863,24 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>3918786000010254030</t>
+          <t>3918786000010254070</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4880,42 +4890,47 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4925,37 +4940,37 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>58800</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4965,44 +4980,49 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>72385</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>3918786000010254028</t>
+          <t>3918786000010254068</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>12-May-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5012,22 +5032,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5037,37 +5057,37 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5077,24 +5097,24 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>3918786000010254026</t>
+          <t>3918786000010254066</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5104,17 +5124,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5124,22 +5149,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5149,37 +5174,37 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5189,24 +5214,24 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>3918786000010254024</t>
+          <t>3918786000010254064</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5216,17 +5241,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5236,22 +5266,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5261,37 +5291,37 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5301,24 +5331,24 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>3918786000010254022</t>
+          <t>3918786000010254062</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5328,17 +5358,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5348,22 +5383,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5373,37 +5408,37 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5413,24 +5448,24 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>3918786000010254020</t>
+          <t>3918786000010254060</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5440,17 +5475,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5460,22 +5500,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5485,27 +5525,27 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5515,7 +5555,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5525,24 +5565,24 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>3918786000010254018</t>
+          <t>3918786000010254058</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5552,109 +5592,114 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>01-May-2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>3918786000010254016</t>
+          <t>3918786000010254056</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5664,97 +5709,102 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>3918786000010254014</t>
+          <t>3918786000010254054</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5766,7 +5816,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>700</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5776,109 +5826,114 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>54300</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>3918786000010254012</t>
+          <t>3918786000010254052</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5888,17 +5943,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5908,22 +5968,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5938,59 +5998,59 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>3918786000010254010</t>
+          <t>3918786000010254050</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6000,17 +6060,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6025,17 +6085,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -6045,12 +6105,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -6065,32 +6125,32 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3918786000010254008</t>
+          <t>3918786000010254032</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6102,32 +6162,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compra de 3 pratos </t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6142,17 +6197,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6162,12 +6217,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -6182,44 +6237,44 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3918786000010254006</t>
+          <t>3918786000010254030</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6229,17 +6284,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6254,17 +6309,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6274,12 +6329,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>58800</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -6294,152 +6349,1501 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>69010</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>3918786000010254004</t>
+          <t>3918786000010254028</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3918786000010254026</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>13845</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>3918786000010254024</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>3918786000010254022</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>3918786000010254020</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>3918786000010254018</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>13150</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>68680</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>3918786000010254016</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>53100</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>68480</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>3918786000010254014</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>16295</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>54300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>68340</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>3918786000010254012</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>55300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>69280</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>3918786000010254010</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>16445</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>68910</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>3918786000010254008</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>16425</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compra de 3 pratos </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>69120</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>3918786000010254006</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>16565</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>69010</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>3918786000010254004</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>JARDIM</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>compra de pratos</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>3918786000010250004</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>54600</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Aurélio António</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>1 Sessão</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
         <is>
           <t>68665</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>3918786000010254002</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -6448,271 +7852,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9032BAA0-63C6-48D6-9B52-7585075162D7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{821690EC-8550-4A59-A6ED-185A56947E0E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2EDBB8B-3EC3-40A7-B256-69E4844328C9}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -7852,4 +7852,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8B9A46-65C0-428A-A514-29B3552FF2BC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C934F88-56F9-47B7-A625-90461FC9B0A1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9985BED6-620A-4FA7-B1FB-960AF24CCEBC}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,22 +504,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -534,64 +529,64 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>21650</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>106760</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3918786000010342032</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>15250</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>91685</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3918786000010267348</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -601,22 +596,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -626,22 +616,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -651,64 +641,64 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>106260</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3918786000010267346</t>
+          <t>3918786000010342030</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,22 +708,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22-May-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -743,22 +728,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010254042</t>
+          <t>3918786000010250004</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -768,64 +753,64 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>88420</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>87615</t>
+          <t>105780</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3918786000010266048</t>
+          <t>3918786000010342028</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -835,22 +820,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>28-May-2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -860,22 +840,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010254042</t>
+          <t>3918786000010250004</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -885,64 +865,64 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>81</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>450</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>86105</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3918786000010266046</t>
+          <t>3918786000010342026</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -952,114 +932,109 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>84170</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>11 Sessão</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>67900</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Manuel Caetano</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>8 Sessão</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>84605</t>
+          <t>103350</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3918786000010266044</t>
+          <t>3918786000010342024</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1069,22 +1044,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>28-May-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1094,22 +1064,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1119,64 +1089,64 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>67900</t>
+          <t>82170</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>10 Sessão</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82605</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3918786000010266042</t>
+          <t>3918786000010342022</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,22 +1156,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1211,22 +1176,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250010</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1236,27 +1201,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>66900</t>
+          <t>82150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1271,17 +1236,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>81505</t>
+          <t>100880</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3918786000010266040</t>
+          <t>3918786000010342020</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1293,7 +1258,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1303,22 +1268,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1328,22 +1288,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250010</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>ORUWERA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1353,64 +1313,64 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>81150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3918786000010266038</t>
+          <t>3918786000010342018</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1420,52 +1380,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>23655</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250012</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1475,17 +1430,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>80100</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1495,39 +1450,39 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>79005</t>
+          <t>98850</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3918786000010266036</t>
+          <t>3918786000010342016</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1537,114 +1492,109 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250012</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>UNIAO FAZ A FORCA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>82100</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>97740</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3918786000010266034</t>
+          <t>3918786000010342014</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1654,114 +1604,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>77600</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>95775</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3918786000010266032</t>
+          <t>3918786000010342012</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1771,22 +1716,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1796,22 +1736,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010254034</t>
+          <t>3918786000010250008</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">União Faz A força </t>
+          <t>MUDANCA DE VIDA</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1821,64 +1761,64 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3918786000010266030</t>
+          <t>3918786000010342010</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1888,7 +1828,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1898,7 +1838,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1913,17 +1853,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010250018</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FUTURO MELHOR</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>FUTURO MELHOR</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1933,12 +1873,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>69850</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1948,49 +1888,49 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>450</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>93965</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3918786000010263168</t>
+          <t>3918786000010342008</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,7 +1940,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2010,7 +1950,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2025,17 +1965,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010250014</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2045,12 +1985,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>60900</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2060,49 +2000,49 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>650</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>93315</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>3918786000010263166</t>
+          <t>3918786000010342006</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2112,7 +2052,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2122,7 +2062,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2137,17 +2077,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010250016</t>
+          <t>3918786000010250018</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2157,12 +2097,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2172,49 +2112,49 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>370</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>73325</t>
+          <t>92945</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>3918786000010263164</t>
+          <t>3918786000010342004</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,7 +2164,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2234,7 +2174,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2249,17 +2189,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010250016</t>
+          <t>3918786000010250018</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MAIS FORCA</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2269,12 +2209,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2284,49 +2224,49 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>72795</t>
+          <t>92945</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3918786000010263162</t>
+          <t>3918786000010342002</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2336,17 +2276,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2356,22 +2301,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010250014</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2381,64 +2326,64 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>72295</t>
+          <t>91685</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>3918786000010263160</t>
+          <t>3918786000010267348</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>680</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2448,109 +2393,114 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>70810</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>3918786000010262006</t>
+          <t>3918786000010267346</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2560,109 +2510,114 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>53200</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>68670</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3918786000010262004</t>
+          <t>3918786000010266048</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2672,17 +2627,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>CURRAPE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2692,22 +2652,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010250004</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>WIKHALIHERA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WIKHALIHERA</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2717,17 +2677,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2737,44 +2697,44 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3918786000010262002</t>
+          <t>3918786000010266046</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2784,12 +2744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2799,12 +2759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2814,32 +2774,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2849,17 +2809,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2869,17 +2829,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>67165</t>
+          <t>84605</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>3918786000010260006</t>
+          <t>3918786000010266044</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2891,7 +2851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,12 +2861,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2916,7 +2876,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2931,32 +2891,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2966,12 +2926,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2981,34 +2941,34 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>82605</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3918786000010260004</t>
+          <t>3918786000010266042</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3018,12 +2978,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3033,7 +2993,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3048,17 +3008,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3068,12 +3028,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3083,49 +3043,49 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>81505</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3918786000010260002</t>
+          <t>3918786000010266040</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3135,12 +3095,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3150,7 +3110,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3165,17 +3125,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3185,12 +3145,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3200,49 +3160,49 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3918786000010254098</t>
+          <t>3918786000010266038</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3252,12 +3212,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3267,7 +3227,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3282,17 +3242,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010254042</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ossuka</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3307,7 +3267,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3317,12 +3277,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3337,29 +3297,29 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>79005</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>3918786000010254096</t>
+          <t>3918786000010266036</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,12 +3329,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3384,7 +3344,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3399,32 +3359,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3434,12 +3394,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3449,34 +3409,34 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>58465</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>3918786000010254094</t>
+          <t>3918786000010266034</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3486,12 +3446,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3501,7 +3461,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3516,17 +3476,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010254040</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Inthela</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3536,12 +3496,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3551,12 +3511,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3566,22 +3526,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>3918786000010254092</t>
+          <t>3918786000010266032</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3593,7 +3553,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3603,12 +3563,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3618,7 +3578,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3633,17 +3593,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010254034</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t xml:space="preserve">União Faz A força </t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3658,7 +3618,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3668,7 +3628,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3683,34 +3643,34 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3918786000010254090</t>
+          <t>3918786000010266030</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3720,22 +3680,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3745,22 +3700,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010254048</t>
+          <t>3918786000010250018</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Somos Caz 2</t>
+          <t>FUTURO MELHOR</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3770,17 +3725,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3790,44 +3745,44 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>76175</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3918786000010254088</t>
+          <t>3918786000010263168</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,22 +3792,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3862,22 +3812,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3887,17 +3837,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3907,44 +3857,44 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>74555</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3918786000010254086</t>
+          <t>3918786000010263166</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3954,22 +3904,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3979,22 +3924,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010254046</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Somos Capaz</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4004,64 +3949,64 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>73325</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3918786000010254084</t>
+          <t>3918786000010263164</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4071,22 +4016,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4096,22 +4036,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250016</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MAIS FORCA</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4121,22 +4061,22 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4146,27 +4086,27 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3918786000010254082</t>
+          <t>3918786000010263162</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4178,7 +4118,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4188,22 +4128,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4213,22 +4148,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250014</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4238,64 +4173,64 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>58700</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>47635</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3918786000010254080</t>
+          <t>3918786000010263160</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4305,114 +4240,109 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>85170</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>9 Sessão</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>70810</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3918786000010254078</t>
+          <t>3918786000010262006</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4422,114 +4352,109 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250006</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>MUATHUNAKA</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>86170</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>45155</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>3918786000010254076</t>
+          <t>3918786000010262004</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4539,22 +4464,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4564,22 +4484,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010250004</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>WIKHALIHERA</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4589,64 +4509,64 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Manuel Caetano</t>
+          <t>Aurélio António</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>43645</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3918786000010254074</t>
+          <t>3918786000010262002</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4656,12 +4576,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4671,12 +4591,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4686,22 +4606,22 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4711,7 +4631,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4721,49 +4641,49 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3918786000010254072</t>
+          <t>3918786000010260006</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4773,12 +4693,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4788,7 +4708,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4803,22 +4723,22 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010254044</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Poupança da Sorte</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4828,7 +4748,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4838,12 +4758,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4853,34 +4773,34 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>3918786000010254070</t>
+          <t>3918786000010260004</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4890,12 +4810,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4905,47 +4825,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3918786000010254040</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Inthela</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Inthela</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Ribaue</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3918786000010254036</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Wiwanana</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4955,64 +4875,64 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>3918786000010254068</t>
+          <t>3918786000010260002</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5022,7 +4942,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5037,17 +4957,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5062,7 +4982,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5072,49 +4992,49 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>8 Sessão</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>3918786000010254066</t>
+          <t>3918786000010254098</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5124,12 +5044,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5139,7 +5059,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5154,17 +5074,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254042</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Ossuka</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5179,7 +5099,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5189,49 +5109,49 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>3918786000010254064</t>
+          <t>3918786000010254096</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5241,12 +5161,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5256,7 +5176,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5271,22 +5191,22 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010254036</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Wiwanana</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5296,7 +5216,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -5306,12 +5226,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5321,7 +5241,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5331,17 +5251,17 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>3918786000010254062</t>
+          <t>3918786000010254094</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -5358,12 +5278,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5373,7 +5293,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5388,17 +5308,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254040</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Inthela</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5408,12 +5328,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -5423,22 +5343,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5448,24 +5368,24 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>3918786000010254060</t>
+          <t>3918786000010254092</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5475,12 +5395,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5490,7 +5410,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5505,17 +5425,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5525,12 +5445,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5540,49 +5460,49 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>55990</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3918786000010254090</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2460</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>31665</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>3918786000010254058</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5592,12 +5512,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5607,7 +5527,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5622,17 +5542,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254048</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Caz 2</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5642,12 +5562,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -5657,12 +5577,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5672,7 +5592,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5682,24 +5602,24 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>3918786000010254056</t>
+          <t>3918786000010254088</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>940</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5709,12 +5629,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5724,7 +5644,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5739,17 +5659,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5759,12 +5679,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5774,12 +5694,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5789,7 +5709,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5799,24 +5719,24 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>26615</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>3918786000010254054</t>
+          <t>3918786000010254086</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5826,12 +5746,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5841,7 +5761,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5856,17 +5776,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254046</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Somos Capaz</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5876,12 +5796,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5891,12 +5811,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5906,7 +5826,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5916,24 +5836,24 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>3918786000010254052</t>
+          <t>3918786000010254084</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5943,12 +5863,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5958,7 +5878,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5973,17 +5893,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010254038</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ochutha Ossuka</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5998,7 +5918,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -6008,12 +5928,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>7 Sessão</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6023,7 +5943,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6033,24 +5953,24 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>48925</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>3918786000010254050</t>
+          <t>3918786000010254082</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6060,17 +5980,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6080,22 +6005,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -6105,37 +6030,37 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6145,24 +6070,24 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3918786000010254032</t>
+          <t>3918786000010254080</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6172,17 +6097,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6192,22 +6122,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6217,37 +6147,37 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6257,24 +6187,24 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3918786000010254030</t>
+          <t>3918786000010254078</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6284,17 +6214,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6304,22 +6239,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010250008</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>MUDANCA DE VIDA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6329,37 +6264,37 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>58800</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6369,24 +6304,24 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>72385</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>3918786000010254028</t>
+          <t>3918786000010254076</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6396,17 +6331,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6416,22 +6356,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6441,37 +6381,37 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6481,24 +6421,24 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>3918786000010254026</t>
+          <t>3918786000010254074</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6508,17 +6448,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6528,22 +6473,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000010250010</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ORUWERA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6553,27 +6498,27 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6583,7 +6528,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6593,24 +6538,24 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>3918786000010254024</t>
+          <t>3918786000010254072</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6620,17 +6565,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMARIESSA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6640,22 +6590,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254044</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Poupança da Sorte</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6665,37 +6615,37 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6705,12 +6655,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>3918786000010254022</t>
+          <t>3918786000010254070</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -6722,7 +6672,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6732,42 +6682,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>13-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6777,37 +6732,37 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6817,44 +6772,49 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>3918786000010254020</t>
+          <t>3918786000010254068</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>12-May-2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6864,22 +6824,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000010250012</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>UNIAO FAZ A FORCA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6889,37 +6849,37 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6929,24 +6889,24 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>3918786000010254018</t>
+          <t>3918786000010254066</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6956,102 +6916,107 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>7 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>3918786000010254016</t>
+          <t>3918786000010254064</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -7068,47 +7033,52 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254036</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Wiwanana</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7118,59 +7088,59 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>6 Sessão</t>
+          <t>1 Sessão</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>3918786000010254014</t>
+          <t>3918786000010254062</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7180,109 +7150,114 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>54300</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>5 Sessão</t>
+          <t>6 Sessão</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>3918786000010254012</t>
+          <t>3918786000010254060</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7292,17 +7267,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7312,22 +7292,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7337,64 +7317,64 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>4 Sessão</t>
+          <t>5 Sessão</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>3918786000010254010</t>
+          <t>3918786000010254058</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7404,17 +7384,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>01-May-2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7424,22 +7409,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -7449,89 +7434,89 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>89</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>3 Sessão</t>
+          <t>4 Sessão</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>3918786000010254008</t>
+          <t>3918786000010254056</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compra de 3 pratos </t>
+          <t>0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7541,22 +7526,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7566,64 +7551,64 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2 Sessão</t>
+          <t>3 Sessão</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>3918786000010254006</t>
+          <t>3918786000010254054</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>700</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7633,17 +7618,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7653,22 +7643,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000010250006</t>
+          <t>3918786000010254038</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>MUATHUNAKA</t>
+          <t>Ochutha Ossuka</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7678,172 +7668,1974 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Aurélio António</t>
+          <t>Manuel Caetano</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1 Sessão</t>
+          <t>2 Sessão</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>69010</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>3918786000010254004</t>
+          <t>3918786000010254052</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3918786000010254038</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ochutha Ossuka</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>25500</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Manuel Caetano</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>21145</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>3918786000010254050</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>3918786000010254032</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>18145</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>3918786000010254030</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3918786000010250008</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>MUDANCA DE VIDA</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>58800</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>72385</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>3918786000010254028</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>3918786000010254026</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3918786000010250010</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ORUWERA</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>13845</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>3918786000010254024</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>3918786000010254022</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>3918786000010254020</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NICANE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3918786000010250012</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>UNIAO FAZ A FORCA</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>3918786000010254018</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>83170</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>7 Sessão</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>13150</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>68680</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>3918786000010254016</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>87670</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>6 Sessão</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>68480</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>3918786000010254014</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>16295</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>89170</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>5 Sessão</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>68340</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>3918786000010254012</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>55300</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>4 Sessão</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>69280</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>3918786000010254010</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>16445</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>3 Sessão</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>68910</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>3918786000010254008</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>16425</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compra de 3 pratos </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2 Sessão</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>69120</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>3918786000010254006</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16565</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3918786000010250006</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>MUATHUNAKA</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Aurélio António</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>1 Sessão</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>69010</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>3918786000010254004</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>JARDIM</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>compra de pratos</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>3918786000010250004</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>WIKHALIHERA</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>54600</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Aurélio António</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>1 Sessão</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
         <is>
           <t>68665</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>3918786000010254002</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -8110,13 +9902,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8B9A46-65C0-428A-A514-29B3552FF2BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003B9758-F14F-4D9E-AE2E-7CB4507CB322}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C934F88-56F9-47B7-A625-90461FC9B0A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470208B3-EFA2-4331-A27C-A6A594FEA7B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9985BED6-620A-4FA7-B1FB-960AF24CCEBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81947C70-0EE2-444A-B405-75472FB167A9}"/>
 </file>